--- a/artfynd/A 3234-2025 artfynd.xlsx
+++ b/artfynd/A 3234-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -793,9 +793,651 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>136951559</v>
+      </c>
+      <c r="B3" t="n">
+        <v>99270</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Bodsjöbyn, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>494539</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6965040</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136951559</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136957210</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99270</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bodsjöbyn, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>494535</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6965053</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136957210</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136957208</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99355</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bodsjöbyn, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>494540</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6965049</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136957208</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136957209</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99377</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bodsjöbyn, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>494538</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6965051</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136957209</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136957211</v>
+      </c>
+      <c r="B7" t="n">
+        <v>110070</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220204</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Slåtterfibbla</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bodsjöbyn, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>494532</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6965057</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136957211</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136957212</v>
+      </c>
+      <c r="B8" t="n">
+        <v>110070</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220204</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Slåtterfibbla</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bodsjöbyn, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>494542</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6965051</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson, Ulf Swenson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136957212</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3234-2025 artfynd.xlsx
+++ b/artfynd/A 3234-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>136951559</v>
       </c>
       <c r="B3" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>136957210</v>
       </c>
       <c r="B4" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>136957208</v>
       </c>
       <c r="B5" t="n">
-        <v>99355</v>
+        <v>99361</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>136957209</v>
       </c>
       <c r="B6" t="n">
-        <v>99377</v>
+        <v>99383</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>136957211</v>
       </c>
       <c r="B7" t="n">
-        <v>110070</v>
+        <v>110076</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>136957212</v>
       </c>
       <c r="B8" t="n">
-        <v>110070</v>
+        <v>110076</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 3234-2025 artfynd.xlsx
+++ b/artfynd/A 3234-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>136951559</v>
       </c>
       <c r="B3" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>136957210</v>
       </c>
       <c r="B4" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>136957208</v>
       </c>
       <c r="B5" t="n">
-        <v>99361</v>
+        <v>99363</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>136957209</v>
       </c>
       <c r="B6" t="n">
-        <v>99383</v>
+        <v>99385</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>136957211</v>
       </c>
       <c r="B7" t="n">
-        <v>110076</v>
+        <v>110078</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>136957212</v>
       </c>
       <c r="B8" t="n">
-        <v>110076</v>
+        <v>110078</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 3234-2025 artfynd.xlsx
+++ b/artfynd/A 3234-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>136951559</v>
       </c>
       <c r="B3" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>136957210</v>
       </c>
       <c r="B4" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>136957208</v>
       </c>
       <c r="B5" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>136957209</v>
       </c>
       <c r="B6" t="n">
-        <v>99385</v>
+        <v>99386</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>136957211</v>
       </c>
       <c r="B7" t="n">
-        <v>110078</v>
+        <v>110079</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>136957212</v>
       </c>
       <c r="B8" t="n">
-        <v>110078</v>
+        <v>110079</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 3234-2025 artfynd.xlsx
+++ b/artfynd/A 3234-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>136951559</v>
       </c>
       <c r="B3" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>136957210</v>
       </c>
       <c r="B4" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>136957208</v>
       </c>
       <c r="B5" t="n">
-        <v>99364</v>
+        <v>99370</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>136957209</v>
       </c>
       <c r="B6" t="n">
-        <v>99386</v>
+        <v>99392</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>136957211</v>
       </c>
       <c r="B7" t="n">
-        <v>110079</v>
+        <v>110085</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>136957212</v>
       </c>
       <c r="B8" t="n">
-        <v>110079</v>
+        <v>110085</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 3234-2025 artfynd.xlsx
+++ b/artfynd/A 3234-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>136951559</v>
       </c>
       <c r="B3" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>136957210</v>
       </c>
       <c r="B4" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>136957208</v>
       </c>
       <c r="B5" t="n">
-        <v>99370</v>
+        <v>99374</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>136957209</v>
       </c>
       <c r="B6" t="n">
-        <v>99392</v>
+        <v>99396</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>136957211</v>
       </c>
       <c r="B7" t="n">
-        <v>110085</v>
+        <v>110089</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>136957212</v>
       </c>
       <c r="B8" t="n">
-        <v>110085</v>
+        <v>110089</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 3234-2025 artfynd.xlsx
+++ b/artfynd/A 3234-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>136951559</v>
       </c>
       <c r="B3" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>136957210</v>
       </c>
       <c r="B4" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>136957208</v>
       </c>
       <c r="B5" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>136957209</v>
       </c>
       <c r="B6" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>136957211</v>
       </c>
       <c r="B7" t="n">
-        <v>110089</v>
+        <v>110091</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>136957212</v>
       </c>
       <c r="B8" t="n">
-        <v>110089</v>
+        <v>110091</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 3234-2025 artfynd.xlsx
+++ b/artfynd/A 3234-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>136951559</v>
       </c>
       <c r="B3" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>136957210</v>
       </c>
       <c r="B4" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>136957208</v>
       </c>
       <c r="B5" t="n">
-        <v>99376</v>
+        <v>99378</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>136957209</v>
       </c>
       <c r="B6" t="n">
-        <v>99398</v>
+        <v>99400</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>136957211</v>
       </c>
       <c r="B7" t="n">
-        <v>110091</v>
+        <v>110093</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>136957212</v>
       </c>
       <c r="B8" t="n">
-        <v>110091</v>
+        <v>110093</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 3234-2025 artfynd.xlsx
+++ b/artfynd/A 3234-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>136951559</v>
       </c>
       <c r="B3" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>136957210</v>
       </c>
       <c r="B4" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>136957208</v>
       </c>
       <c r="B5" t="n">
-        <v>99378</v>
+        <v>99391</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>136957209</v>
       </c>
       <c r="B6" t="n">
-        <v>99400</v>
+        <v>99413</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>136957211</v>
       </c>
       <c r="B7" t="n">
-        <v>110093</v>
+        <v>110106</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>136957212</v>
       </c>
       <c r="B8" t="n">
-        <v>110093</v>
+        <v>110106</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 3234-2025 artfynd.xlsx
+++ b/artfynd/A 3234-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>136951559</v>
       </c>
       <c r="B3" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>136957210</v>
       </c>
       <c r="B4" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>136957208</v>
       </c>
       <c r="B5" t="n">
-        <v>99391</v>
+        <v>99393</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>136957209</v>
       </c>
       <c r="B6" t="n">
-        <v>99413</v>
+        <v>99415</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>136957211</v>
       </c>
       <c r="B7" t="n">
-        <v>110106</v>
+        <v>110108</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>136957212</v>
       </c>
       <c r="B8" t="n">
-        <v>110106</v>
+        <v>110108</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 3234-2025 artfynd.xlsx
+++ b/artfynd/A 3234-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>136951559</v>
       </c>
       <c r="B3" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>136957210</v>
       </c>
       <c r="B4" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>136957208</v>
       </c>
       <c r="B5" t="n">
-        <v>99393</v>
+        <v>99396</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>136957209</v>
       </c>
       <c r="B6" t="n">
-        <v>99415</v>
+        <v>99418</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>136957211</v>
       </c>
       <c r="B7" t="n">
-        <v>110108</v>
+        <v>110113</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>136957212</v>
       </c>
       <c r="B8" t="n">
-        <v>110108</v>
+        <v>110113</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 3234-2025 artfynd.xlsx
+++ b/artfynd/A 3234-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>136951559</v>
       </c>
       <c r="B3" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>136957210</v>
       </c>
       <c r="B4" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>136957208</v>
       </c>
       <c r="B5" t="n">
-        <v>99396</v>
+        <v>99406</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>136957209</v>
       </c>
       <c r="B6" t="n">
-        <v>99418</v>
+        <v>99428</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>136957211</v>
       </c>
       <c r="B7" t="n">
-        <v>110113</v>
+        <v>110134</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>136957212</v>
       </c>
       <c r="B8" t="n">
-        <v>110113</v>
+        <v>110134</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 3234-2025 artfynd.xlsx
+++ b/artfynd/A 3234-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>136951559</v>
       </c>
       <c r="B3" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>136957210</v>
       </c>
       <c r="B4" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>136957208</v>
       </c>
       <c r="B5" t="n">
-        <v>99406</v>
+        <v>99407</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>136957209</v>
       </c>
       <c r="B6" t="n">
-        <v>99428</v>
+        <v>99429</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>136957211</v>
       </c>
       <c r="B7" t="n">
-        <v>110134</v>
+        <v>110135</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>136957212</v>
       </c>
       <c r="B8" t="n">
-        <v>110134</v>
+        <v>110135</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 3234-2025 artfynd.xlsx
+++ b/artfynd/A 3234-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>136951559</v>
       </c>
       <c r="B3" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>136957210</v>
       </c>
       <c r="B4" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>136957208</v>
       </c>
       <c r="B5" t="n">
-        <v>99407</v>
+        <v>99412</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>136957209</v>
       </c>
       <c r="B6" t="n">
-        <v>99429</v>
+        <v>99434</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>136957211</v>
       </c>
       <c r="B7" t="n">
-        <v>110135</v>
+        <v>110140</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>136957212</v>
       </c>
       <c r="B8" t="n">
-        <v>110135</v>
+        <v>110140</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 3234-2025 artfynd.xlsx
+++ b/artfynd/A 3234-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>136951559</v>
       </c>
       <c r="B3" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>136957210</v>
       </c>
       <c r="B4" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>136957208</v>
       </c>
       <c r="B5" t="n">
-        <v>99412</v>
+        <v>99414</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>136957209</v>
       </c>
       <c r="B6" t="n">
-        <v>99434</v>
+        <v>99436</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>136957211</v>
       </c>
       <c r="B7" t="n">
-        <v>110140</v>
+        <v>110143</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>136957212</v>
       </c>
       <c r="B8" t="n">
-        <v>110140</v>
+        <v>110143</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 3234-2025 artfynd.xlsx
+++ b/artfynd/A 3234-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>136951559</v>
       </c>
       <c r="B3" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>136957210</v>
       </c>
       <c r="B4" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>136957208</v>
       </c>
       <c r="B5" t="n">
-        <v>99414</v>
+        <v>99420</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>136957209</v>
       </c>
       <c r="B6" t="n">
-        <v>99436</v>
+        <v>99442</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>136957211</v>
       </c>
       <c r="B7" t="n">
-        <v>110143</v>
+        <v>110149</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>136957212</v>
       </c>
       <c r="B8" t="n">
-        <v>110143</v>
+        <v>110149</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 3234-2025 artfynd.xlsx
+++ b/artfynd/A 3234-2025 artfynd.xlsx
@@ -1222,7 +1222,7 @@
         <v>136957211</v>
       </c>
       <c r="B7" t="n">
-        <v>110149</v>
+        <v>110150</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>136957212</v>
       </c>
       <c r="B8" t="n">
-        <v>110149</v>
+        <v>110150</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 3234-2025 artfynd.xlsx
+++ b/artfynd/A 3234-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>136951559</v>
       </c>
       <c r="B3" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>136957210</v>
       </c>
       <c r="B4" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>136957208</v>
       </c>
       <c r="B5" t="n">
-        <v>99420</v>
+        <v>99432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>136957209</v>
       </c>
       <c r="B6" t="n">
-        <v>99442</v>
+        <v>99454</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>136957211</v>
       </c>
       <c r="B7" t="n">
-        <v>110150</v>
+        <v>110162</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>136957212</v>
       </c>
       <c r="B8" t="n">
-        <v>110150</v>
+        <v>110162</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 3234-2025 artfynd.xlsx
+++ b/artfynd/A 3234-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>136951559</v>
       </c>
       <c r="B3" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>136957210</v>
       </c>
       <c r="B4" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>136957208</v>
       </c>
       <c r="B5" t="n">
-        <v>99432</v>
+        <v>99433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>136957209</v>
       </c>
       <c r="B6" t="n">
-        <v>99454</v>
+        <v>99455</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>136957211</v>
       </c>
       <c r="B7" t="n">
-        <v>110162</v>
+        <v>110163</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>136957212</v>
       </c>
       <c r="B8" t="n">
-        <v>110162</v>
+        <v>110163</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 3234-2025 artfynd.xlsx
+++ b/artfynd/A 3234-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>136951559</v>
       </c>
       <c r="B3" t="n">
-        <v>99348</v>
+        <v>99351</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>136957210</v>
       </c>
       <c r="B4" t="n">
-        <v>99348</v>
+        <v>99351</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>136957208</v>
       </c>
       <c r="B5" t="n">
-        <v>99433</v>
+        <v>99436</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>136957209</v>
       </c>
       <c r="B6" t="n">
-        <v>99455</v>
+        <v>99458</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>136957211</v>
       </c>
       <c r="B7" t="n">
-        <v>110163</v>
+        <v>110166</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>136957212</v>
       </c>
       <c r="B8" t="n">
-        <v>110163</v>
+        <v>110166</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 3234-2025 artfynd.xlsx
+++ b/artfynd/A 3234-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>136951559</v>
       </c>
       <c r="B3" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>136957210</v>
       </c>
       <c r="B4" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>136957208</v>
       </c>
       <c r="B5" t="n">
-        <v>99436</v>
+        <v>99437</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>136957209</v>
       </c>
       <c r="B6" t="n">
-        <v>99458</v>
+        <v>99459</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>136957211</v>
       </c>
       <c r="B7" t="n">
-        <v>110166</v>
+        <v>110168</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>136957212</v>
       </c>
       <c r="B8" t="n">
-        <v>110166</v>
+        <v>110168</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 3234-2025 artfynd.xlsx
+++ b/artfynd/A 3234-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>136951559</v>
       </c>
       <c r="B3" t="n">
-        <v>99352</v>
+        <v>99355</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>136957210</v>
       </c>
       <c r="B4" t="n">
-        <v>99352</v>
+        <v>99355</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>136957208</v>
       </c>
       <c r="B5" t="n">
-        <v>99437</v>
+        <v>99440</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>136957209</v>
       </c>
       <c r="B6" t="n">
-        <v>99459</v>
+        <v>99462</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1222,7 +1222,7 @@
         <v>136957211</v>
       </c>
       <c r="B7" t="n">
-        <v>110168</v>
+        <v>110172</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>136957212</v>
       </c>
       <c r="B8" t="n">
-        <v>110168</v>
+        <v>110172</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
